--- a/文法（ぶんぽう）/汉语语法.xlsx
+++ b/文法（ぶんぽう）/汉语语法.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9048" firstSheet="4" activeTab="9"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="恋人「こい」" sheetId="4" state="hidden" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="2105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="2113">
   <si>
     <t>会いたい</t>
   </si>
@@ -5978,6 +5978,21 @@
     <t>家里小，加上孩子多，所以没办法好好地休息</t>
   </si>
   <si>
+    <t>有些地方...</t>
+  </si>
+  <si>
+    <t>所々</t>
+  </si>
+  <si>
+    <t>所々+…</t>
+  </si>
+  <si>
+    <t>所々に雪が残る</t>
+  </si>
+  <si>
+    <t>有些地方积了雪</t>
+  </si>
+  <si>
     <t>誰</t>
   </si>
   <si>
@@ -6025,6 +6040,26 @@
         <charset val="128"/>
       </rPr>
       <t>无论哪个人都…</t>
+    </r>
+  </si>
+  <si>
+    <t>誰しも</t>
+  </si>
+  <si>
+    <t>だれしも</t>
+  </si>
+  <si>
+    <r>
+      <t>誰しもわからない：无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="128"/>
+      </rPr>
+      <t>论谁都不懂的知识</t>
     </r>
   </si>
   <si>
@@ -18881,10 +18916,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
@@ -18895,32 +18956,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
+      <color theme="4"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="4"/>
-      <name val="Yu Gothic"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -18931,24 +18973,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="等线"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -18981,11 +19005,10 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="等线"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -18993,6 +19016,18 @@
       <color rgb="FF00B0F0"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -20616,7 +20651,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.6666666666667" customWidth="1"/>
@@ -21289,6 +21324,23 @@
         <v>895</v>
       </c>
     </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>896</v>
+      </c>
+      <c r="B50" t="s">
+        <v>897</v>
+      </c>
+      <c r="C50" t="s">
+        <v>898</v>
+      </c>
+      <c r="D50" t="s">
+        <v>899</v>
+      </c>
+      <c r="E50" t="s">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -21298,7 +21350,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
@@ -21308,135 +21360,146 @@
   <sheetData>
     <row r="1" ht="18" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="C2" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>901</v>
+        <v>906</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>902</v>
+        <v>907</v>
       </c>
       <c r="C3" t="s">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>906</v>
+        <v>911</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>907</v>
+      <c r="A5" s="1" t="s">
+        <v>912</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="C5" s="11"/>
+        <v>913</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="6" ht="18" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>909</v>
+      <c r="A6" s="2" t="s">
+        <v>915</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>910</v>
-      </c>
+        <v>916</v>
+      </c>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" ht="18" spans="1:4">
-      <c r="A7" t="s">
-        <v>911</v>
+      <c r="A7" s="1" t="s">
+        <v>917</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="D7" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:4">
       <c r="A8" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>753</v>
+        <v>920</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D8" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:4">
       <c r="A9" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="D9" t="s">
-        <v>917</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>918</v>
+      <c r="A10" t="s">
+        <v>919</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>921</v>
+        <v>924</v>
+      </c>
+      <c r="D10" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="C11" t="s">
-        <v>924</v>
-      </c>
-      <c r="D11" t="s">
-        <v>925</v>
+        <v>927</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>930</v>
+      </c>
       <c r="B12" s="1" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="C12" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="D12" t="s">
-        <v>928</v>
+        <v>933</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:4">
+      <c r="B13" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" t="s">
+        <v>935</v>
+      </c>
+      <c r="D13" t="s">
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -21474,19 +21537,19 @@
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="27" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>52</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="E2" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
@@ -21494,75 +21557,75 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="E3" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="27" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="D4" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="E4" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="E5" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="B6" s="1" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="E6" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="D7" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="E7" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
@@ -21571,19 +21634,19 @@
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="A9" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="E9" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
@@ -21591,54 +21654,54 @@
         <v>67</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="D10" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="E10" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="E11" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="B12" s="1"/>
       <c r="C12" s="9" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="E12" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="D13" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="E13" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
@@ -21647,69 +21710,69 @@
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="A15" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="D15" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="E15" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="E16" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="18" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="18" spans="1:5">
       <c r="D18" s="1" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="18" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>311</v>
@@ -21731,166 +21794,166 @@
     </row>
     <row r="21" ht="18" spans="1:5">
       <c r="A21" s="27" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="E21" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:5">
       <c r="D22" s="1" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="E22" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:5">
       <c r="A23" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="B23" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C23" t="s">
         <v>854</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="E23" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="C24" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="D24" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="E24" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:5">
       <c r="C25" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="E25" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:5">
       <c r="C26" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="E26" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:5">
       <c r="C27" s="1" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="E27" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:5">
       <c r="C28" s="1" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="E28" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:5">
       <c r="A29" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="E29" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="D31" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="E31" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:5">
       <c r="A32" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="33" ht="18" spans="4:5">
       <c r="D33" s="1" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="E33" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
   </sheetData>
@@ -21926,194 +21989,194 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="41" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="D9" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="E9" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="D10" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="E10" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="D11" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="E11" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>269</v>
@@ -22122,15 +22185,15 @@
         <v>270</v>
       </c>
       <c r="D13" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="E13" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>262</v>
@@ -22139,84 +22202,84 @@
         <v>263</v>
       </c>
       <c r="D14" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="B17" s="13"/>
       <c r="D17" s="1" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="41" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="41" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -22228,19 +22291,19 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="41" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -22249,28 +22312,28 @@
         <v>205</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="E22" s="13"/>
     </row>
     <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="41" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -22279,16 +22342,16 @@
         <v>205</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="41" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>67</v>
@@ -22297,24 +22360,24 @@
         <v>160</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="41" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:5">
@@ -22323,45 +22386,45 @@
         <v>205</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="E27" s="13"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="41" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="41" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -22370,28 +22433,28 @@
         <v>205</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="41" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -22402,10 +22465,10 @@
         <v>205</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -22414,27 +22477,27 @@
         <v>205</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="41" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -22443,10 +22506,10 @@
         <v>205</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -22455,37 +22518,37 @@
         <v>205</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="37" ht="18.75" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
     </row>
     <row r="38" ht="18.75" spans="1:5">
       <c r="A38" s="7"/>
       <c r="B38" s="13"/>
       <c r="D38" s="40" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="E38" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -22496,105 +22559,105 @@
         <v>205</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D39" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="E39" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="D40" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="D42" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="E42" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7"/>
       <c r="B43" s="13"/>
       <c r="C43" s="1" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="D43" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="E43" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="41" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="13" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -22602,235 +22665,235 @@
         <v>67</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="41" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="41" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="41" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="B50" s="42" t="s">
         <v>67</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="41" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="B51" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="41" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="41" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="13" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="E55" t="s">
-        <v>1200</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="13" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="D56" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="13" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>177</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:5">
       <c r="A60" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D61" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="E61" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -22838,13 +22901,13 @@
         <v>217</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="E62" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -22852,58 +22915,58 @@
         <v>217</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="E63" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="E64" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="B65" s="19"/>
       <c r="D65" s="1" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="E65" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="B66" s="43" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:5">
       <c r="A67" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>217</v>
@@ -22912,7 +22975,7 @@
         <v>566</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>568</v>
@@ -22961,91 +23024,91 @@
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="27" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:5">
       <c r="A3" s="27" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="A4" s="27"/>
       <c r="C4" s="1" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="A5" s="38" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="27"/>
       <c r="C6" s="1" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="E6" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="27"/>
       <c r="C7" s="1" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>205</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="E8" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
@@ -23053,65 +23116,65 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="E9" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="25" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D10" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="E10" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:5">
       <c r="A12" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>217</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:5">
       <c r="D13" s="1" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="E13" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:5">
@@ -23119,41 +23182,41 @@
         <v>217</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="E14" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:5">
       <c r="C15" s="1" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="D15" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="E15" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:5">
       <c r="A16" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="B16" t="s">
         <v>205</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="E16" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:5">
@@ -23161,64 +23224,64 @@
         <v>205</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="D17" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="E17" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:5">
       <c r="A18" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B18" t="s">
         <v>205</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="D18" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="E18" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:5">
       <c r="A19" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="B19" t="s">
         <v>458</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="D19" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="E19" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="20" ht="18.75" spans="1:5">
       <c r="A20" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="B20" t="s">
         <v>205</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="E20" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="21" ht="18.75" spans="1:5">
@@ -23226,42 +23289,42 @@
         <v>205</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="D21" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:5">
       <c r="A22" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="B22" t="s">
         <v>205</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="E22" s="36"/>
     </row>
     <row r="23" ht="18" spans="1:5">
       <c r="A23" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="B23" t="s">
         <v>458</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="E23" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:5">
@@ -23269,13 +23332,13 @@
         <v>458</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="E24" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:5">
@@ -23283,30 +23346,30 @@
         <v>458</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="E25" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:5">
       <c r="A26" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="B26" t="s">
         <v>458</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D26" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="E26" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -23342,19 +23405,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="33" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="E2" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="F2"/>
     </row>
@@ -23362,28 +23425,28 @@
       <c r="A3" s="33"/>
       <c r="B3" s="12"/>
       <c r="D3" s="1" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="E3" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="33" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="E4" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="F4"/>
     </row>
@@ -23392,193 +23455,193 @@
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5" s="1" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="E5" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="7" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2"/>
       <c r="B10" s="12"/>
       <c r="D10" s="1" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="7" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2"/>
       <c r="B12" s="12"/>
       <c r="D12" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="E12" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="E13" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="27" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="E14" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="27"/>
       <c r="B15" s="19" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="E15" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="27"/>
       <c r="B16" s="19"/>
       <c r="D16" s="1" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="E16" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -23587,97 +23650,97 @@
         <v>205</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="D17" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="E17" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="E18" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="E19" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1379</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="B21" s="12"/>
       <c r="C21" s="1" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="D23" s="1" t="s">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -23685,80 +23748,80 @@
         <v>67</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>1402</v>
+        <v>1410</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
     </row>
   </sheetData>
@@ -23793,140 +23856,140 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="31" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="32" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="31" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="33" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="E5" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="33" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1428</v>
+        <v>1436</v>
       </c>
       <c r="D9" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1430</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1433</v>
+        <v>1441</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -23952,7 +24015,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>225</v>
@@ -23966,156 +24029,156 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>1436</v>
+        <v>1444</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1440</v>
+        <v>1448</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1441</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="7" t="s">
-        <v>1442</v>
+        <v>1450</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1444</v>
+        <v>1452</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1445</v>
+        <v>1453</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1446</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1454</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" s="1" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1456</v>
+        <v>1464</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1452</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>1458</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1449</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>1459</v>
+        <v>1467</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1460</v>
+        <v>1468</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="D8" s="1" t="s">
-        <v>1462</v>
+        <v>1470</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1463</v>
+        <v>1471</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1461</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="29" t="s">
-        <v>1464</v>
+        <v>1472</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1437</v>
+        <v>1445</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1466</v>
+        <v>1474</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1467</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="29"/>
       <c r="B10" s="5"/>
       <c r="D10" s="9" t="s">
-        <v>1468</v>
+        <v>1476</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1469</v>
+        <v>1477</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1470</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="29"/>
       <c r="B11" s="5"/>
       <c r="D11" s="9" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1472</v>
+        <v>1480</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1473</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -24123,167 +24186,167 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="9" t="s">
-        <v>1474</v>
+        <v>1482</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1448</v>
+        <v>1456</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1475</v>
+        <v>1483</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9"/>
       <c r="D14" s="1" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="D16" s="1" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="D18" s="1" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="D20" s="1" t="s">
-        <v>1495</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>1496</v>
+        <v>1504</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="D22" s="1" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
-        <v>1497</v>
+        <v>1505</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1449</v>
+        <v>1457</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1498</v>
+        <v>1506</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1499</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="D24" s="1" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="7" t="s">
-        <v>1500</v>
+        <v>1508</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="C26" s="30" t="s">
         <v>553</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1502</v>
+        <v>1510</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1503</v>
+        <v>1511</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1504</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -24292,30 +24355,30 @@
       <c r="C27" s="30"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1" t="s">
-        <v>1505</v>
+        <v>1513</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1506</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>1507</v>
+        <v>1515</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="C28" s="30" t="s">
         <v>553</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1510</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -24324,172 +24387,172 @@
       <c r="C29" s="30"/>
       <c r="D29" s="3"/>
       <c r="E29" s="1" t="s">
-        <v>1511</v>
+        <v>1519</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1512</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>1513</v>
+        <v>1521</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>1501</v>
+        <v>1509</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>553</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1514</v>
+        <v>1522</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1515</v>
+        <v>1523</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>553</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1520</v>
+        <v>1528</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1521</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>553</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="1" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>553</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1534</v>
+        <v>1542</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1535</v>
+        <v>1543</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1536</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>1537</v>
+        <v>1545</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1540</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>1541</v>
+        <v>1549</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>1544</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="1" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>1545</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="B40" s="1" t="s">
-        <v>1542</v>
+        <v>1550</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1543</v>
+        <v>1551</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1546</v>
+        <v>1554</v>
       </c>
     </row>
   </sheetData>
@@ -24526,132 +24589,132 @@
     </row>
     <row r="2" ht="18" spans="1:5">
       <c r="A2" s="27" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="B2" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
       <c r="C2" t="s">
-        <v>1549</v>
+        <v>1557</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1550</v>
+        <v>1558</v>
       </c>
       <c r="E2" t="s">
-        <v>1551</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="3" ht="19.2" customHeight="1" spans="1:5">
       <c r="A3" s="27" t="s">
-        <v>1552</v>
+        <v>1560</v>
       </c>
       <c r="B3" t="s">
-        <v>1548</v>
+        <v>1556</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1553</v>
+        <v>1561</v>
       </c>
       <c r="D3" t="s">
-        <v>1554</v>
+        <v>1562</v>
       </c>
       <c r="E3" t="s">
-        <v>1555</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:5">
       <c r="D4" s="1" t="s">
-        <v>1556</v>
+        <v>1564</v>
       </c>
       <c r="E4" t="s">
-        <v>1557</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:5">
       <c r="C5" s="1" t="s">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="D5" t="s">
-        <v>1559</v>
+        <v>1567</v>
       </c>
       <c r="E5" t="s">
-        <v>1560</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:5">
       <c r="A6" s="27" t="s">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="B6" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1561</v>
+        <v>1569</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1562</v>
+        <v>1570</v>
       </c>
       <c r="E6" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:5">
       <c r="A7" s="27"/>
       <c r="C7" s="28"/>
       <c r="D7" s="1" t="s">
-        <v>1564</v>
+        <v>1572</v>
       </c>
       <c r="E7" t="s">
-        <v>1565</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:5">
       <c r="A8" s="27" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
       <c r="E8" t="s">
-        <v>1563</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:5">
       <c r="C9" s="1" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="E9" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:5">
       <c r="C10" s="1" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
       <c r="E10" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:5">
       <c r="B11" s="1" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1577</v>
+        <v>1585</v>
       </c>
     </row>
   </sheetData>
@@ -24891,22 +24954,22 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1578</v>
+        <v>1586</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1579</v>
+        <v>1587</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1580</v>
+        <v>1588</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>226</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1582</v>
+        <v>1590</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>48</v>
@@ -24914,227 +24977,227 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1584</v>
+        <v>1592</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1587</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
-        <v>1588</v>
+        <v>1596</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1590</v>
+        <v>1598</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1592</v>
+        <v>1600</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1593</v>
+        <v>1601</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1595</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="5" t="s">
-        <v>1596</v>
+        <v>1604</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1597</v>
+        <v>1605</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1598</v>
+        <v>1606</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1602</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="5" t="s">
-        <v>1603</v>
+        <v>1611</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1604</v>
+        <v>1612</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1605</v>
+        <v>1613</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1599</v>
+        <v>1607</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1607</v>
+        <v>1615</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1608</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="5" t="s">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1589</v>
+        <v>1597</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1610</v>
+        <v>1618</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1611</v>
+        <v>1619</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1612</v>
+        <v>1620</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1613</v>
+        <v>1621</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1614</v>
+        <v>1622</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1615</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="5" t="s">
-        <v>1616</v>
+        <v>1624</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1617</v>
+        <v>1625</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1619</v>
+        <v>1627</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1622</v>
+        <v>1630</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1623</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>1624</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="25" t="s">
-        <v>1625</v>
+        <v>1633</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1627</v>
+        <v>1635</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1628</v>
+        <v>1636</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1629</v>
+        <v>1637</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1630</v>
+        <v>1638</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2"/>
       <c r="B13" s="26"/>
       <c r="D13" s="1" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2"/>
       <c r="B14" s="26"/>
       <c r="D14" s="9" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2"/>
       <c r="B15" s="26"/>
       <c r="C15" s="1" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
       <c r="D15" t="s">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="E15" t="s">
-        <v>1642</v>
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -25159,7 +25222,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>225</v>
@@ -25176,95 +25239,95 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>1645</v>
+        <v>1653</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1646</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>1647</v>
+        <v>1655</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>1650</v>
+        <v>1658</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1651</v>
+        <v>1659</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1654</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>1655</v>
+        <v>1663</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1656</v>
+        <v>1664</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1657</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>1658</v>
+        <v>1666</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>1660</v>
+        <v>1668</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1661</v>
+        <v>1669</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1662</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>1663</v>
+        <v>1671</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1659</v>
+        <v>1667</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>1664</v>
+        <v>1672</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1665</v>
+        <v>1673</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1666</v>
+        <v>1674</v>
       </c>
     </row>
   </sheetData>
@@ -25299,326 +25362,326 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="20" t="s">
-        <v>1667</v>
+        <v>1675</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>1668</v>
+        <v>1676</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>1669</v>
+        <v>1677</v>
       </c>
       <c r="F1" s="14"/>
       <c r="I1" s="14" t="s">
-        <v>1670</v>
+        <v>1678</v>
       </c>
       <c r="J1" s="20"/>
       <c r="K1" s="12" t="s">
-        <v>1671</v>
+        <v>1679</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>1672</v>
+        <v>1680</v>
       </c>
       <c r="M1" s="14"/>
     </row>
     <row r="2" spans="1:15">
       <c r="B2" s="20" t="s">
-        <v>1673</v>
+        <v>1681</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>1674</v>
+        <v>1682</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1675</v>
+        <v>1683</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>1676</v>
+        <v>1684</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>1677</v>
+        <v>1685</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>1678</v>
+        <v>1686</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>1679</v>
+        <v>1687</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>1680</v>
+        <v>1688</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>1682</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="B3" s="13" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>1684</v>
+        <v>1692</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="13" t="s">
-        <v>1685</v>
+        <v>1693</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>1686</v>
+        <v>1694</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="14" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
       <c r="K3" s="14"/>
       <c r="L3" s="13" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="4" ht="20.4" customHeight="1" spans="1:15">
       <c r="A4" s="13" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="13" t="s">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>1698</v>
+        <v>1706</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14" t="s">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="K4" s="14"/>
     </row>
     <row r="6" customHeight="1" spans="1:15">
       <c r="D6" s="20" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="F6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="13" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>1716</v>
+        <v>1724</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>1719</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="13" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>1721</v>
+        <v>1729</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="13" t="s">
-        <v>1722</v>
+        <v>1730</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="12" t="s">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>1725</v>
+        <v>1733</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>1726</v>
+        <v>1734</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="13" t="s">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="M8" s="20" t="s">
-        <v>1728</v>
+        <v>1736</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>1729</v>
+        <v>1737</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>1730</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="D10" s="20" t="s">
-        <v>1731</v>
+        <v>1739</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1732</v>
+        <v>1740</v>
       </c>
       <c r="F10" s="14"/>
       <c r="I10" s="14" t="s">
-        <v>1733</v>
+        <v>1741</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="13" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1683</v>
+        <v>1691</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>1738</v>
+        <v>1746</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>1739</v>
+        <v>1747</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>1740</v>
+        <v>1748</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>1741</v>
+        <v>1749</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>1742</v>
+        <v>1750</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>1743</v>
+        <v>1751</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>1744</v>
+        <v>1752</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>1745</v>
+        <v>1753</v>
       </c>
       <c r="M11" s="20" t="s">
-        <v>1746</v>
+        <v>1754</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>1747</v>
+        <v>1755</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>1748</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="13" t="s">
-        <v>1749</v>
+        <v>1757</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1750</v>
+        <v>1758</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="13" t="s">
-        <v>1751</v>
+        <v>1759</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="12" t="s">
-        <v>1753</v>
+        <v>1761</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>1754</v>
+        <v>1762</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="K12" s="16"/>
     </row>
     <row r="14" spans="1:15">
       <c r="C14" s="13" t="s">
-        <v>1753</v>
+        <v>1761</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1756</v>
+        <v>1764</v>
       </c>
     </row>
   </sheetData>
@@ -25656,74 +25719,74 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
       <c r="A1" s="12" t="s">
-        <v>1757</v>
+        <v>1765</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>1760</v>
+        <v>1768</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>1761</v>
+        <v>1769</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1762</v>
+        <v>1770</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>1763</v>
+        <v>1771</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>281</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="2" ht="36" spans="1:9">
       <c r="A2" s="12" t="s">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1765</v>
+        <v>1773</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>1766</v>
+        <v>1774</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
       <c r="G2" s="15" t="s">
-        <v>1767</v>
+        <v>1775</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>1768</v>
+        <v>1776</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>1750</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="3" s="12" customFormat="1"/>
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="12" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1770</v>
+        <v>1778</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="15" t="s">
-        <v>1771</v>
+        <v>1779</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>1772</v>
+        <v>1780</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -25733,12 +25796,12 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="12" t="s">
-        <v>1773</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="12" t="s">
-        <v>1774</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -25746,45 +25809,45 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="19" t="s">
-        <v>1775</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="19" t="s">
-        <v>1776</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="13" t="s">
-        <v>1777</v>
+        <v>1785</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1778</v>
+        <v>1786</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="12" t="s">
-        <v>1780</v>
+        <v>1788</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1781</v>
+        <v>1789</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1782</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="12" t="s">
-        <v>1783</v>
+        <v>1791</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1785</v>
+        <v>1793</v>
       </c>
     </row>
   </sheetData>
@@ -25817,27 +25880,27 @@
   <sheetData>
     <row r="1" ht="18" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>1786</v>
+        <v>1794</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>1787</v>
+        <v>1795</v>
       </c>
       <c r="G1" s="1"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" ht="18" spans="1:15">
       <c r="A2" t="s">
-        <v>1788</v>
+        <v>1796</v>
       </c>
       <c r="B2" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="D2" t="s">
-        <v>1621</v>
+        <v>1629</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -25846,16 +25909,16 @@
     </row>
     <row r="3" ht="18" spans="1:15">
       <c r="A3" t="s">
-        <v>1791</v>
+        <v>1799</v>
       </c>
       <c r="B3" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -25864,19 +25927,19 @@
     </row>
     <row r="4" ht="18" spans="1:15">
       <c r="A4" t="s">
-        <v>1793</v>
+        <v>1801</v>
       </c>
       <c r="B4" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1794</v>
+        <v>1802</v>
       </c>
       <c r="E4" t="s">
-        <v>1795</v>
+        <v>1803</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
@@ -25885,13 +25948,13 @@
     </row>
     <row r="5" ht="18" spans="1:15">
       <c r="A5" t="s">
-        <v>1796</v>
+        <v>1804</v>
       </c>
       <c r="B5" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>145</v>
@@ -25903,16 +25966,16 @@
     </row>
     <row r="6" ht="18" spans="1:15">
       <c r="A6" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>1798</v>
       </c>
-      <c r="B6" t="s">
-        <v>1789</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1790</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>1799</v>
+        <v>1807</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
@@ -25921,13 +25984,13 @@
     </row>
     <row r="7" ht="18" spans="1:15">
       <c r="B7" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1"/>
@@ -25936,13 +25999,13 @@
     </row>
     <row r="8" ht="18" spans="1:15">
       <c r="B8" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="D8" t="s">
-        <v>1801</v>
+        <v>1809</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="1"/>
@@ -25951,19 +26014,19 @@
     </row>
     <row r="9" ht="18" spans="1:15">
       <c r="A9" t="s">
-        <v>1802</v>
+        <v>1810</v>
       </c>
       <c r="B9" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="E9" t="s">
-        <v>1805</v>
+        <v>1813</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="1"/>
@@ -25971,16 +26034,16 @@
     </row>
     <row r="10" ht="18" spans="1:15">
       <c r="A10" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="B10" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1807</v>
+        <v>1815</v>
       </c>
       <c r="E10" t="s">
         <v>295</v>
@@ -25994,32 +26057,32 @@
     </row>
     <row r="11" ht="18" spans="1:15">
       <c r="B11" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="E11" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
     <row r="12" ht="18" spans="1:15">
       <c r="B12" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="E12" t="s">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -26029,16 +26092,16 @@
     </row>
     <row r="13" ht="18" spans="1:15">
       <c r="B13" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1812</v>
+        <v>1820</v>
       </c>
       <c r="E13" t="s">
-        <v>1813</v>
+        <v>1821</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -26046,16 +26109,16 @@
     </row>
     <row r="14" ht="18" spans="1:15">
       <c r="A14" t="s">
-        <v>1814</v>
+        <v>1822</v>
       </c>
       <c r="B14" t="s">
-        <v>1815</v>
+        <v>1823</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="1"/>
@@ -26063,51 +26126,51 @@
     </row>
     <row r="15" ht="18" spans="1:15">
       <c r="A15" t="s">
-        <v>1817</v>
+        <v>1825</v>
       </c>
       <c r="B15" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" ht="18" spans="1:15">
       <c r="A16" t="s">
-        <v>1818</v>
+        <v>1826</v>
       </c>
       <c r="B16" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1820</v>
+        <v>1828</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
     <row r="17" ht="18" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>1822</v>
+        <v>1830</v>
       </c>
       <c r="B17" t="s">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1825</v>
+        <v>1833</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -26116,48 +26179,48 @@
     </row>
     <row r="18" ht="18" spans="1:11">
       <c r="A18" s="11" t="s">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="B18" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="E18" t="s">
-        <v>1830</v>
+        <v>1838</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
     <row r="19" ht="18" spans="1:11">
       <c r="A19" s="11" t="s">
-        <v>1831</v>
+        <v>1839</v>
       </c>
       <c r="B19" t="s">
-        <v>1832</v>
+        <v>1840</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1834</v>
+        <v>1842</v>
       </c>
       <c r="E19" t="s">
-        <v>1835</v>
+        <v>1843</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="10"/>
     </row>
     <row r="20" ht="18" spans="1:11">
       <c r="D20" t="s">
-        <v>1836</v>
+        <v>1844</v>
       </c>
       <c r="E20" t="s">
-        <v>1837</v>
+        <v>1845</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -26172,53 +26235,53 @@
     </row>
     <row r="22" ht="18" spans="1:11">
       <c r="A22" t="s">
-        <v>1838</v>
+        <v>1846</v>
       </c>
       <c r="B22" t="s">
-        <v>1839</v>
+        <v>1847</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1840</v>
+        <v>1848</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1841</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:11">
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>1842</v>
+        <v>1850</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1843</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:11">
       <c r="A24" t="s">
-        <v>1844</v>
+        <v>1852</v>
       </c>
       <c r="B24" t="s">
-        <v>1845</v>
+        <v>1853</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1846</v>
+        <v>1854</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1847</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:11">
       <c r="D25" s="1" t="s">
-        <v>1848</v>
+        <v>1856</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1849</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:11">
@@ -26227,19 +26290,19 @@
     </row>
     <row r="27" ht="18" spans="1:11">
       <c r="A27" t="s">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1851</v>
+        <v>1859</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="H27" s="1"/>
       <c r="J27" s="1"/>
@@ -26247,37 +26310,37 @@
     </row>
     <row r="28" ht="18" spans="1:11">
       <c r="D28" s="1" t="s">
-        <v>1854</v>
+        <v>1862</v>
       </c>
       <c r="E28" t="s">
-        <v>1855</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:11">
       <c r="A29" s="11" t="s">
-        <v>1856</v>
+        <v>1864</v>
       </c>
       <c r="B29" t="s">
-        <v>1857</v>
+        <v>1865</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D29" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="E29" t="s">
-        <v>1859</v>
+        <v>1867</v>
       </c>
       <c r="H29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" ht="18" spans="1:11">
       <c r="D30" s="1" t="s">
-        <v>1860</v>
+        <v>1868</v>
       </c>
       <c r="E30" t="s">
-        <v>1861</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:11">
@@ -26285,73 +26348,73 @@
     </row>
     <row r="32" ht="18" spans="1:11">
       <c r="A32" t="s">
-        <v>1862</v>
+        <v>1870</v>
       </c>
       <c r="B32" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1863</v>
+        <v>1871</v>
       </c>
       <c r="E32" t="s">
-        <v>1864</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:6">
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>1865</v>
+        <v>1873</v>
       </c>
       <c r="E33" t="s">
-        <v>1866</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:6">
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>1867</v>
+        <v>1875</v>
       </c>
       <c r="E34" t="s">
-        <v>1868</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:6">
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
       <c r="E35" t="s">
-        <v>1870</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="36" ht="18" spans="1:6">
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>1871</v>
+        <v>1879</v>
       </c>
       <c r="E36" t="s">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" ht="18" spans="1:6">
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>1873</v>
+        <v>1881</v>
       </c>
       <c r="E37" t="s">
-        <v>1874</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:6">
       <c r="D38" s="1" t="s">
-        <v>1875</v>
+        <v>1883</v>
       </c>
       <c r="E38" t="s">
-        <v>1876</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="39" ht="18" spans="1:6">
@@ -26359,31 +26422,31 @@
     </row>
     <row r="40" ht="18" spans="1:6">
       <c r="A40" t="s">
-        <v>1877</v>
+        <v>1885</v>
       </c>
       <c r="B40" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1878</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="41" ht="18" spans="1:6">
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>1879</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:6">
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>1880</v>
+        <v>1888</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1881</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="43" ht="18" spans="1:6">
@@ -26392,25 +26455,25 @@
     </row>
     <row r="44" ht="18" spans="1:6">
       <c r="A44" t="s">
-        <v>1882</v>
+        <v>1890</v>
       </c>
       <c r="B44" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1880</v>
+        <v>1888</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1883</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="45" ht="18" spans="1:6">
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>1884</v>
+        <v>1892</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -26421,116 +26484,116 @@
     </row>
     <row r="47" ht="18" spans="1:6">
       <c r="A47" t="s">
-        <v>1885</v>
+        <v>1893</v>
       </c>
       <c r="B47" t="s">
-        <v>1886</v>
+        <v>1894</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>573</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1887</v>
+        <v>1895</v>
       </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" ht="18" spans="1:6">
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>1888</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="49" ht="18" spans="1:6">
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>1889</v>
+        <v>1897</v>
       </c>
       <c r="E49" s="1"/>
     </row>
     <row r="50" ht="18" spans="1:6">
       <c r="A50" t="s">
-        <v>1890</v>
+        <v>1898</v>
       </c>
       <c r="B50" t="s">
-        <v>1891</v>
+        <v>1899</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1892</v>
+        <v>1900</v>
       </c>
       <c r="E50" s="1"/>
     </row>
     <row r="51" ht="18" spans="1:6">
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>1893</v>
+        <v>1901</v>
       </c>
       <c r="E51" s="1"/>
     </row>
     <row r="52" ht="18" spans="1:6">
       <c r="A52" t="s">
-        <v>1894</v>
+        <v>1902</v>
       </c>
       <c r="B52" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1896</v>
+        <v>1904</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1897</v>
+        <v>1905</v>
       </c>
       <c r="E52" s="1"/>
     </row>
     <row r="53" ht="18" spans="1:6">
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>1898</v>
+        <v>1906</v>
       </c>
       <c r="E53" s="1"/>
     </row>
     <row r="54" ht="18" spans="1:6">
       <c r="A54" t="s">
-        <v>1899</v>
+        <v>1907</v>
       </c>
       <c r="B54" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="E54" s="1"/>
     </row>
     <row r="55" ht="18" spans="1:6">
       <c r="D55" s="1" t="s">
-        <v>1902</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="56" ht="18" spans="1:6">
       <c r="A56" t="s">
-        <v>1903</v>
+        <v>1911</v>
       </c>
       <c r="B56" t="s">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1833</v>
+        <v>1841</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>1905</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:6">
       <c r="D57" s="1" t="s">
-        <v>1906</v>
+        <v>1914</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1907</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="58" ht="18" spans="1:6">
@@ -26539,28 +26602,28 @@
     </row>
     <row r="59" ht="18" spans="1:6">
       <c r="A59" t="s">
-        <v>1908</v>
+        <v>1916</v>
       </c>
       <c r="B59" t="s">
-        <v>1909</v>
+        <v>1917</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1910</v>
+        <v>1918</v>
       </c>
       <c r="E59" s="1"/>
     </row>
     <row r="60" ht="18" spans="1:6">
       <c r="A60" t="s">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1912</v>
+        <v>1920</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>1913</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="61" ht="18" spans="1:6">
@@ -26569,49 +26632,49 @@
     </row>
     <row r="62" ht="18" spans="1:6">
       <c r="A62" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1916</v>
+        <v>1924</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1917</v>
+        <v>1925</v>
       </c>
       <c r="F62" s="1"/>
     </row>
     <row r="63" ht="18" spans="1:6">
       <c r="B63" s="1" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1918</v>
+        <v>1926</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="F63" s="1"/>
     </row>
     <row r="64" ht="18" spans="1:6">
       <c r="B64" s="1" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="E64" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
       <c r="F64" s="1"/>
     </row>
@@ -26636,10 +26699,10 @@
   <sheetData>
     <row r="1" ht="19.8" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1923</v>
+        <v>1931</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>226</v>
@@ -26647,589 +26710,589 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>1924</v>
+        <v>1932</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1926</v>
+        <v>1934</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1927</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1930</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>753</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1934</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="D5" s="1" t="s">
-        <v>1935</v>
+        <v>1943</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1936</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="D6" s="1" t="s">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1938</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>1939</v>
+        <v>1947</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>753</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1940</v>
+        <v>1948</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1941</v>
+        <v>1949</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1942</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>1943</v>
+        <v>1951</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1944</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1945</v>
+        <v>1953</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1946</v>
+        <v>1954</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1947</v>
+        <v>1955</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1948</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5"/>
       <c r="B10" s="3" t="s">
-        <v>1945</v>
+        <v>1953</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1949</v>
+        <v>1957</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1950</v>
+        <v>1958</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1951</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="7" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1945</v>
+        <v>1953</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="7" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>741</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1956</v>
+        <v>1964</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1957</v>
+        <v>1965</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1958</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="7" t="s">
-        <v>1959</v>
+        <v>1967</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>741</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1956</v>
+        <v>1964</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>846</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1963</v>
+        <v>1971</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1965</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="D15" s="1" t="s">
-        <v>1966</v>
+        <v>1974</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1967</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="D16" s="1" t="s">
-        <v>1968</v>
+        <v>1976</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1969</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1974</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5"/>
       <c r="D18" s="1" t="s">
-        <v>1975</v>
+        <v>1983</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1976</v>
+        <v>1984</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1977</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>1978</v>
+        <v>1986</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>753</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1979</v>
+        <v>1987</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1836</v>
+        <v>1844</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1980</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="5" t="s">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1984</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="5" t="s">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1986</v>
+        <v>1994</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1987</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
-        <v>1988</v>
+        <v>1996</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>765</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1989</v>
+        <v>1997</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1990</v>
+        <v>1998</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1991</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
-        <v>1992</v>
+        <v>2000</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1994</v>
+        <v>2002</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1996</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5"/>
       <c r="C24" s="1" t="s">
-        <v>1997</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="5"/>
       <c r="C25" s="1" t="s">
-        <v>1998</v>
+        <v>2006</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1999</v>
+        <v>2007</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2000</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="5"/>
       <c r="C26" s="1" t="s">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>2003</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="5" t="s">
-        <v>2004</v>
+        <v>2012</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2008</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="7" t="s">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>2013</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>2020</v>
+        <v>2028</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>2021</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="D32" s="1" t="s">
-        <v>2026</v>
+        <v>2034</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>2027</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="D33" s="8" t="s">
-        <v>2028</v>
+        <v>2036</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>2029</v>
+        <v>2037</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>2030</v>
+        <v>2038</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>2031</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="5" t="s">
-        <v>2032</v>
+        <v>2040</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2033</v>
+        <v>2041</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2034</v>
+        <v>2042</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>2035</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="C35" s="1" t="s">
-        <v>2036</v>
+        <v>2044</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>2037</v>
+        <v>2045</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>2038</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="5"/>
       <c r="C36" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>2039</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>2040</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="5" t="s">
-        <v>2041</v>
+        <v>2049</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>2042</v>
+        <v>2050</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2043</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="D38" s="1" t="s">
-        <v>2044</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>2045</v>
+        <v>2053</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>698</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>2046</v>
+        <v>2054</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>2047</v>
+        <v>2055</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2048</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="B41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>2049</v>
+        <v>2057</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>2050</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>2051</v>
+        <v>2059</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>2052</v>
+        <v>2060</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2053</v>
+        <v>2061</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2054</v>
+        <v>2062</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>2055</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="D43" s="1" t="s">
-        <v>2056</v>
+        <v>2064</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>2057</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>2058</v>
+        <v>2066</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>741</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>2059</v>
+        <v>2067</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>2060</v>
+        <v>2068</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>2061</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="D45" s="1" t="s">
-        <v>2062</v>
+        <v>2070</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>2063</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>2064</v>
+        <v>2072</v>
       </c>
     </row>
   </sheetData>
@@ -27254,13 +27317,13 @@
   <sheetData>
     <row r="1" ht="18" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>2065</v>
+        <v>2073</v>
       </c>
       <c r="B1" t="s">
         <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2066</v>
+        <v>2074</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>226</v>
@@ -27268,17 +27331,17 @@
     </row>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>2067</v>
+        <v>2075</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>807</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>2068</v>
+        <v>2076</v>
       </c>
       <c r="E2" t="s">
-        <v>2069</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
@@ -27286,125 +27349,125 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>2070</v>
+        <v>2078</v>
       </c>
       <c r="E3" t="s">
-        <v>2071</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>2072</v>
+        <v>2080</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2073</v>
+        <v>2081</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2074</v>
+        <v>2082</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2075</v>
+        <v>2083</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>2076</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2077</v>
+        <v>2085</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2078</v>
+        <v>2086</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2074</v>
+        <v>2082</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2080</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>2077</v>
+        <v>2085</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2082</v>
+        <v>2090</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>2083</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="B7" s="1" t="s">
-        <v>2084</v>
+        <v>2092</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2085</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="B8" s="1" t="s">
-        <v>2086</v>
+        <v>2094</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2079</v>
+        <v>2087</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2087</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>2088</v>
+        <v>2096</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>573</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2089</v>
+        <v>2097</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>351</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2090</v>
+        <v>2098</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>2091</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="E10" s="1" t="s">
-        <v>2092</v>
+        <v>2100</v>
       </c>
       <c r="F10" t="s">
-        <v>2093</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" t="s">
-        <v>2088</v>
+        <v>2096</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2094</v>
+        <v>2102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2089</v>
+        <v>2097</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>355</v>
@@ -27440,21 +27503,21 @@
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="D14" s="1" t="s">
-        <v>2095</v>
+        <v>2103</v>
       </c>
       <c r="E14" t="s">
-        <v>2096</v>
+        <v>2104</v>
       </c>
       <c r="F14" t="s">
-        <v>2097</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" t="s">
-        <v>2098</v>
+        <v>2106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2099</v>
+        <v>2107</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>466</v>
@@ -27463,13 +27526,13 @@
         <v>476</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2100</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>2101</v>
+        <v>2109</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>480</v>
@@ -27481,19 +27544,19 @@
     <row r="17" ht="18" spans="2:5">
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>2102</v>
+        <v>2110</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>483</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2103</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="18" ht="18" spans="2:5">
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
-        <v>2104</v>
+        <v>2112</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>486</v>
